--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2402,7 +2402,7 @@
 </t>
   </si>
   <si>
-    <t>Slicing nach dem Komponenten-Code.</t>
+    <t>Slicing by the component code.</t>
   </si>
   <si>
     <t>Observation.component.id</t>
@@ -2539,7 +2539,7 @@
     <t>Observation.component:menge.value[x]:valueQuantity</t>
   </si>
   <si>
-    <t>Count per field of view, UCUM unit /[HPF]. For open bounds Quantity.comparator is used, e.g. '&lt;10/HPF' as comparator = '&lt;', value = 10.</t>
+    <t>Count per high-power field, UCUM unit /[HPF]. For open bounds Quantity.comparator is used, e.g. '&lt;10/HPF' as comparator = '&lt;', value = 10.</t>
   </si>
   <si>
     <t>Observation.component:menge.value[x]:valueQuantity.id</t>
@@ -2597,7 +2597,7 @@
     <t>Observation.component:menge.value[x]:valueRange</t>
   </si>
   <si>
-    <t>Count per field of view as an interval, UCUM unit /[HPF] — e.g. '10-25/HPF' as low = 10, high = 25.</t>
+    <t>Count per high-power field as an interval, UCUM unit /[HPF] — e.g. '10-25/HPF' as low = 10, high = 25.</t>
   </si>
   <si>
     <t>Observation.component:menge.value[x]:valueRange.id</t>

--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
